--- a/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -938,7 +938,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1011,7 +1010,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1084,7 +1082,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1157,7 +1154,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1230,7 +1226,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1303,7 +1298,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -1376,7 +1370,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1449,7 +1442,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1522,7 +1514,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1595,7 +1586,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1668,7 +1658,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1741,7 +1730,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1814,7 +1802,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1887,7 +1874,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1960,7 +1946,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -2033,7 +2018,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -2106,7 +2090,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -2179,7 +2162,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -2252,7 +2234,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -2325,7 +2306,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -2398,7 +2378,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -2471,7 +2450,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2544,7 +2522,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -2617,7 +2594,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -2690,7 +2666,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2763,7 +2738,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2836,7 +2810,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -2909,7 +2882,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -2982,7 +2954,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -3055,7 +3026,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" t="inlineStr">
@@ -3128,7 +3098,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -3201,7 +3170,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -3274,7 +3242,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -3347,7 +3314,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -3420,7 +3386,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -3493,7 +3458,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -3566,7 +3530,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -3639,7 +3602,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" t="inlineStr">
@@ -3712,7 +3674,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -3785,7 +3746,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -3858,7 +3818,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -3931,7 +3890,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -4004,7 +3962,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -4077,7 +4034,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -4150,7 +4106,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" t="inlineStr">
@@ -4223,7 +4178,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" t="inlineStr">
@@ -4296,7 +4250,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -4369,7 +4322,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -4442,7 +4394,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -4515,7 +4466,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -4588,7 +4538,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -4661,7 +4610,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -4734,7 +4682,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -4807,7 +4754,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -4880,7 +4826,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -4953,7 +4898,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" t="inlineStr">
@@ -5026,7 +4970,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -5099,7 +5042,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -5172,7 +5114,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -5245,7 +5186,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" t="inlineStr">
@@ -5318,7 +5258,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -5391,7 +5330,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" t="inlineStr">
@@ -5464,12 +5402,295 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
-    </row>
-    <row r="68" ht="28" customHeight="1"/>
-    <row r="69" ht="28" customHeight="1"/>
-    <row r="70" ht="28" customHeight="1"/>
-    <row r="71" ht="28" customHeight="1"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>INS-AUS-0003</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Australian Catholic University</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Australian Catholic University</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>North Sydney</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.acu.edu.au/</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>city_au_geonames_2154855</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>INS-AUS-0004</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>The University of Notre Dame Australia</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>The University of Notre Dame Australia</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fremantle</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://www.notredame.edu.au/</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>city_au_geonames_2071223</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>INS-AUS-0014</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Western Sydney University</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Western Sydney University</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Penrith</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://www.westernsydney.edu.au/</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>city_au_geonames_2153471</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>INS-AUS-0039</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Avondale University</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Avondale University</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cooranbong</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.avondale.edu.au/</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>city_au_geonames_2170456</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
     <row r="72" ht="28" customHeight="1"/>
     <row r="73" ht="28" customHeight="1"/>
   </sheetData>
@@ -6700,7 +6921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6788,17 +7009,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INS-AUS-0003</t>
+          <t>INS-AUS-0023</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australian Catholic University</t>
+          <t>University of the Sunshine Coast</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Australian Catholic University</t>
+          <t>University of the Sunshine Coast</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6813,7 +7034,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>North Sydney</t>
+          <t>Sippy Downs</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6833,7 +7054,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.acu.edu.au/</t>
+          <t>https://www.usc.edu.au/</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -6841,8 +7062,6 @@
           <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -6850,49 +7069,49 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INS-AUS-0004</t>
+          <t>INS-PNG-0004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The University of Notre Dame Australia</t>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The University of Notre Dame Australia</t>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fremantle</t>
+          <t>Vudal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6902,16 +7121,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.notredame.edu.au/</t>
+          <t>https://www.unre.ac.pg/</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -6919,283 +7136,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INS-AUS-0014</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Western Sydney University</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Western Sydney University</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Penrith</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://www.westernsydney.edu.au/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INS-AUS-0023</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>University of the Sunshine Coast</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>University of the Sunshine Coast</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sippy Downs</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://www.usc.edu.au/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>INS-AUS-0039</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avondale University</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Avondale University</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cooranbong</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://www.avondale.edu.au/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>INS-PNG-0004</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Vudal</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://www.unre.ac.pg/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>

--- a/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
@@ -784,7 +784,6 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -6921,7 +6920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7006,140 +7005,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INS-AUS-0023</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>University of the Sunshine Coast</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>University of the Sunshine Coast</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sippy Downs</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://www.usc.edu.au/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INS-PNG-0004</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vudal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.unre.ac.pg/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
@@ -784,6 +784,7 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -6920,7 +6921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7005,6 +7006,140 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INS-AUS-0023</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sippy Downs</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.usc.edu.au/</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INS-PNG-0004</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vudal</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.unre.ac.pg/</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5691,7 +5691,83 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="28" customHeight="1"/>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>INS-AUS-0023</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sippy Downs</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.usc.edu.au/</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>city_au_official_sippy_downs</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PRIMARY_ADDRESS_SEARCH_INDEX_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
     <row r="73" ht="28" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
@@ -6921,7 +6997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7009,37 +7085,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INS-AUS-0023</t>
+          <t>INS-PNG-0004</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>University of the Sunshine Coast</t>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>University of the Sunshine Coast</t>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sippy Downs</t>
+          <t>Vudal</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7054,12 +7130,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.usc.edu.au/</t>
+          <t>https://www.unre.ac.pg/</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://www.teqsa.gov.au/national-register | https://universitiesaustralia.edu.au/our-universities/university-profiles/</t>
+          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -7068,73 +7144,6 @@
         </is>
       </c>
       <c r="P2" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INS-PNG-0004</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vudal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.unre.ac.pg/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>

--- a/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/Oceania_Universities_Import_English_14_Countries_COMPLETE.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,6 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -5768,7 +5767,83 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="28" customHeight="1"/>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>INS-PNG-0004</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Papua New Guinea University of Natural Resources and Environment</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Vudal</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.unre.ac.pg/</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>city_pg_official_vudal</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>PG-EBR</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -6997,7 +7072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7082,73 +7157,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INS-PNG-0004</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Papua New Guinea University of Natural Resources and Environment</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Vudal</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://www.unre.ac.pg/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://apply.dherst.gov.pg/ | https://web.dherst.gov.pg/</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
